--- a/R_Codes/DataSummary/Archaea/Sample_Type/Archaea_Summary_Order_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_Type/Archaea_Summary_Order_by_Sample_Type.xlsx
@@ -477,10 +477,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>18.5202533685736</v>
+        <v>18.5201013097571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.505976770488784</v>
+        <v>0.505976909932865</v>
       </c>
     </row>
     <row r="3">
@@ -491,10 +491,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>16.5372588192262</v>
+        <v>16.5329845316454</v>
       </c>
       <c r="D3" t="n">
-        <v>3.04154912689679</v>
+        <v>3.04051963402742</v>
       </c>
     </row>
     <row r="4">
@@ -505,10 +505,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>12.4378584460888</v>
+        <v>12.4382553298214</v>
       </c>
       <c r="D4" t="n">
-        <v>0.428313229449437</v>
+        <v>0.428325745678215</v>
       </c>
     </row>
     <row r="5">
@@ -519,10 +519,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>12.3021921641972</v>
+        <v>12.3026594588541</v>
       </c>
       <c r="D5" t="n">
-        <v>0.680026350575475</v>
+        <v>0.680014840542453</v>
       </c>
     </row>
     <row r="6">
@@ -533,10 +533,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>11.7452341318612</v>
+        <v>11.7458348323098</v>
       </c>
       <c r="D6" t="n">
-        <v>1.37682566368649</v>
+        <v>1.37689345146925</v>
       </c>
     </row>
     <row r="7">
@@ -547,10 +547,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>6.25422579699541</v>
+        <v>6.25509725438493</v>
       </c>
       <c r="D7" t="n">
-        <v>3.99436845805551</v>
+        <v>3.99503421260845</v>
       </c>
     </row>
     <row r="8">
@@ -561,10 +561,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>5.47371315766783</v>
+        <v>5.47426332536916</v>
       </c>
       <c r="D8" t="n">
-        <v>0.725016650401825</v>
+        <v>0.725104134642925</v>
       </c>
     </row>
     <row r="9">
@@ -575,10 +575,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>3.83852280450956</v>
+        <v>3.83946933329157</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0622087400615458</v>
+        <v>0.062235005592485</v>
       </c>
     </row>
     <row r="10">
@@ -589,10 +589,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>3.11433185157042</v>
+        <v>3.11454051303145</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0384232790596677</v>
+        <v>0.0384252193784699</v>
       </c>
     </row>
     <row r="11">
@@ -603,10 +603,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>2.19994636630155</v>
+        <v>2.1998961256231</v>
       </c>
       <c r="D11" t="n">
-        <v>0.107160564694792</v>
+        <v>0.107160590329108</v>
       </c>
     </row>
     <row r="12">
@@ -617,10 +617,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>1.46754394593324</v>
+        <v>1.46756821441988</v>
       </c>
       <c r="D12" t="n">
-        <v>0.221908676469357</v>
+        <v>0.221914596352504</v>
       </c>
     </row>
     <row r="13">
@@ -631,10 +631,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>1.46564892526542</v>
+        <v>1.46612663342029</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0466877372539877</v>
+        <v>0.0467043258433747</v>
       </c>
     </row>
     <row r="14">
@@ -645,10 +645,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.939262261327925</v>
+        <v>0.939235706664847</v>
       </c>
       <c r="D14" t="n">
-        <v>0.076588972054449</v>
+        <v>0.0765853287362225</v>
       </c>
     </row>
     <row r="15">
@@ -659,10 +659,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>0.922485621046044</v>
+        <v>0.922428448465171</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0956601710709274</v>
+        <v>0.0956434026846114</v>
       </c>
     </row>
     <row r="16">
@@ -673,10 +673,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>0.702726037156627</v>
+        <v>0.702697770525482</v>
       </c>
       <c r="D16" t="n">
-        <v>0.187953862659956</v>
+        <v>0.187943863450388</v>
       </c>
     </row>
     <row r="17">
@@ -687,10 +687,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>0.642172015204204</v>
+        <v>0.642169123069737</v>
       </c>
       <c r="D17" t="n">
-        <v>0.165207216080162</v>
+        <v>0.165199823432465</v>
       </c>
     </row>
     <row r="18">
@@ -701,10 +701,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.373053088548069</v>
+        <v>0.373104243580127</v>
       </c>
       <c r="D18" t="n">
-        <v>0.115024472265287</v>
+        <v>0.115042827780335</v>
       </c>
     </row>
     <row r="19">
@@ -715,10 +715,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>0.242175367283282</v>
+        <v>0.242160708289927</v>
       </c>
       <c r="D19" t="n">
-        <v>0.105117748515762</v>
+        <v>0.105102080516384</v>
       </c>
     </row>
     <row r="20">
@@ -729,7 +729,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.212351047265552</v>
+        <v>0.212345660707166</v>
       </c>
       <c r="D20"/>
     </row>
@@ -741,10 +741,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.140690285136584</v>
+        <v>0.140685141227975</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0128404769835274</v>
+        <v>0.0128378141578971</v>
       </c>
     </row>
     <row r="22">
@@ -755,10 +755,10 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.139326797297523</v>
+        <v>0.139357882061933</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00657364646947169</v>
+        <v>0.00657574523047377</v>
       </c>
     </row>
     <row r="23">
@@ -769,10 +769,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.114960544008385</v>
+        <v>0.114961862604409</v>
       </c>
       <c r="D23" t="n">
-        <v>0.032622598907635</v>
+        <v>0.0326241618178361</v>
       </c>
     </row>
     <row r="24">
@@ -783,10 +783,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0757661709457359</v>
+        <v>0.0757499067335201</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0524181217803904</v>
+        <v>0.0524055170092779</v>
       </c>
     </row>
     <row r="25">
@@ -797,7 +797,7 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0730903125241704</v>
+        <v>0.0730940892896911</v>
       </c>
       <c r="D25"/>
     </row>
@@ -809,7 +809,7 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0301708776892948</v>
+        <v>0.0301647251607637</v>
       </c>
       <c r="D26"/>
     </row>
@@ -821,7 +821,7 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0230510669255519</v>
+        <v>0.0230564187299055</v>
       </c>
       <c r="D27"/>
     </row>
@@ -833,10 +833,10 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00727727790575996</v>
+        <v>0.00727632488319893</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0014999434261184</v>
+        <v>0.00149874617041298</v>
       </c>
     </row>
     <row r="29">
@@ -847,7 +847,7 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00252748841842708</v>
+        <v>0.00252893753007687</v>
       </c>
       <c r="D29"/>
     </row>
@@ -859,7 +859,7 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00218396312648901</v>
+        <v>0.00218618854804676</v>
       </c>
       <c r="D30"/>
     </row>
@@ -896,10 +896,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>54.1129255454368</v>
+        <v>54.2903931518093</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2494138186117</v>
+        <v>10.2900236788944</v>
       </c>
     </row>
     <row r="3">
@@ -910,10 +910,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>24.0089554710508</v>
+        <v>23.9509554304592</v>
       </c>
       <c r="D3" t="n">
-        <v>0.238203648998989</v>
+        <v>0.237575554856321</v>
       </c>
     </row>
     <row r="4">
@@ -924,10 +924,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>5.60580054516845</v>
+        <v>5.56924494107659</v>
       </c>
       <c r="D4" t="n">
-        <v>0.580672928149858</v>
+        <v>0.578594848887287</v>
       </c>
     </row>
     <row r="5">
@@ -938,10 +938,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>3.06739139740554</v>
+        <v>3.01882625814057</v>
       </c>
       <c r="D5" t="n">
-        <v>0.444867388771745</v>
+        <v>0.434510459085714</v>
       </c>
     </row>
     <row r="6">
@@ -952,10 +952,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>2.38068014178256</v>
+        <v>2.37341644833467</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0576789885094573</v>
+        <v>0.0575256732831891</v>
       </c>
     </row>
     <row r="7">
@@ -966,10 +966,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>2.3714300919777</v>
+        <v>2.36654661741218</v>
       </c>
       <c r="D7" t="n">
-        <v>0.619525480262922</v>
+        <v>0.618148293180579</v>
       </c>
     </row>
     <row r="8">
@@ -980,10 +980,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2498010685236</v>
+        <v>2.24377837702993</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0709713743826551</v>
+        <v>0.0707567477334005</v>
       </c>
     </row>
     <row r="9">
@@ -994,10 +994,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1.48665146850221</v>
+        <v>1.48241692400949</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0487943680005873</v>
+        <v>0.0486365079780662</v>
       </c>
     </row>
     <row r="10">
@@ -1008,10 +1008,10 @@
         <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>1.44257685920316</v>
+        <v>1.43906660564869</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0493847440262116</v>
+        <v>0.0492352887412829</v>
       </c>
     </row>
     <row r="11">
@@ -1022,10 +1022,10 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>1.32716241454733</v>
+        <v>1.3240618689994</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0559850266460437</v>
+        <v>0.055841320783689</v>
       </c>
     </row>
     <row r="12">
@@ -1036,10 +1036,10 @@
         <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>0.509258253215987</v>
+        <v>0.508486644638778</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0463705023945219</v>
+        <v>0.0462714911307914</v>
       </c>
     </row>
     <row r="13">
@@ -1050,10 +1050,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>0.418237393102326</v>
+        <v>0.417060694344558</v>
       </c>
       <c r="D13" t="n">
-        <v>0.164955414331459</v>
+        <v>0.164491248245208</v>
       </c>
     </row>
     <row r="14">
@@ -1064,10 +1064,10 @@
         <v>30</v>
       </c>
       <c r="C14" t="n">
-        <v>0.351612305902911</v>
+        <v>0.351483052903812</v>
       </c>
       <c r="D14" t="n">
-        <v>0.155646830278538</v>
+        <v>0.155638374117642</v>
       </c>
     </row>
     <row r="15">
@@ -1078,10 +1078,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>0.202909538947346</v>
+        <v>0.200269945495604</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0110467151095926</v>
+        <v>0.0107855099896259</v>
       </c>
     </row>
     <row r="16">
@@ -1092,10 +1092,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>0.18885004415727</v>
+        <v>0.188888925600684</v>
       </c>
       <c r="D16" t="n">
-        <v>0.081184499936407</v>
+        <v>0.0812062953531732</v>
       </c>
     </row>
     <row r="17">
@@ -1106,7 +1106,7 @@
         <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>0.122043620490263</v>
+        <v>0.121669959620492</v>
       </c>
       <c r="D17"/>
     </row>
@@ -1118,10 +1118,10 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>0.031028231306782</v>
+        <v>0.0309894801565336</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00584097358048779</v>
+        <v>0.00583147820982544</v>
       </c>
     </row>
     <row r="19">
@@ -1132,7 +1132,7 @@
         <v>26</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0296149408341879</v>
+        <v>0.0295685255181075</v>
       </c>
       <c r="D19"/>
     </row>
@@ -1144,10 +1144,10 @@
         <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0287377020477431</v>
+        <v>0.0286789171097611</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00414494693494354</v>
+        <v>0.0041369753964699</v>
       </c>
     </row>
     <row r="21">
@@ -1158,10 +1158,10 @@
         <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0214075508501126</v>
+        <v>0.0213649759054163</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00582731581784547</v>
+        <v>0.00581331564038483</v>
       </c>
     </row>
     <row r="22">
@@ -1172,10 +1172,10 @@
         <v>19</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0112981671212124</v>
+        <v>0.0112786167875188</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00220970538097561</v>
+        <v>0.00220594438459289</v>
       </c>
     </row>
     <row r="23">
@@ -1186,7 +1186,7 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>0.010897695032061</v>
+        <v>0.0108696982802279</v>
       </c>
       <c r="D23"/>
     </row>
@@ -1198,7 +1198,7 @@
         <v>31</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00848451746553975</v>
+        <v>0.00846763661958161</v>
       </c>
       <c r="D24"/>
     </row>
@@ -1210,7 +1210,7 @@
         <v>29</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00336541783215633</v>
+        <v>0.00335957532414269</v>
       </c>
       <c r="D25"/>
     </row>
@@ -1222,7 +1222,7 @@
         <v>35</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00333010546463304</v>
+        <v>0.00331873303929328</v>
       </c>
       <c r="D26"/>
     </row>
@@ -1234,7 +1234,7 @@
         <v>24</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00251404162474268</v>
+        <v>0.0025108092006458</v>
       </c>
       <c r="D27"/>
     </row>
@@ -1246,7 +1246,7 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00161919639026515</v>
+        <v>0.0016136667785894</v>
       </c>
       <c r="D28"/>
     </row>
@@ -1258,7 +1258,7 @@
         <v>36</v>
       </c>
       <c r="C29" t="n">
-        <v>0.000961590582669442</v>
+        <v>0.000959892825720676</v>
       </c>
       <c r="D29"/>
     </row>
@@ -1270,7 +1270,7 @@
         <v>37</v>
       </c>
       <c r="C30" t="n">
-        <v>0.000454684033659048</v>
+        <v>0.000453626930754705</v>
       </c>
       <c r="D30"/>
     </row>
